--- a/business-libraries/test-data/home_school/tool.xlsx
+++ b/business-libraries/test-data/home_school/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AJ8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,96 +430,102 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>HS_RX_001</v>
       </c>
       <c r="B2" t="str">
-        <v>家长会沟通模板</v>
+        <v>先跟后带话术卡</v>
       </c>
       <c r="C2" t="str">
-        <v>沟通模板</v>
+        <v>先跟后带</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
       </c>
       <c r="E2" t="str">
-        <v>exercise</v>
+        <v>script</v>
       </c>
       <c r="F2" t="str">
         <v>all</v>
@@ -528,96 +534,105 @@
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>感到情绪即将失控、疲惫难以恢复时</v>
+        <v>家长有情绪但尚未升级，需要先稳住关系</v>
       </c>
       <c r="I2" t="str">
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>沟通质量与信任双低</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="K2" t="str">
-        <v>home_school,orange,communication</v>
+        <v>关系容器不足</v>
       </c>
       <c r="L2" t="str">
-        <v>情绪恢复</v>
+        <v>home_school,container</v>
       </c>
       <c r="M2" t="str">
-        <v>1) 离开当前情境 2) 三轮缓慢呼吸 3) 命名情绪 4) 选最小行动</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="N2" t="str">
-        <v>现在先停三分钟，这三分钟只属于你自己。</v>
-      </c>
-      <c r="O2" t="str">
-        <v>单次可下降 1-2 分主观压力值</v>
+        <v>在不认同内容的前提下承接情绪</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">先复述家长的担心，用他的原话
+表达理解而非认同：「我能感受到您现在很担心」
+把话题引向可核实的事实
+约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="P2" t="str">
-        <v>3 分钟</v>
+        <v>我能感受到您现在很担心。我们先把事实逐项核实，再一起决定下一步。</v>
       </c>
       <c r="Q2" t="str">
-        <v>每日 1-2 次，连续 7 天</v>
+        <v>单次沟通内情绪明显降温</v>
       </c>
       <c r="R2" t="str">
-        <v>7</v>
+        <v>10 分钟</v>
       </c>
       <c r="S2" t="str">
-        <v>不用于替代危机处置；出现自伤念头或持续失眠时须转介心理专员</v>
+        <v>按需</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>不要在情绪高点解释责任归属；不要承诺未核实的事项</v>
       </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>HS_RX_004</v>
+        <v/>
       </c>
       <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
         <v>B</v>
       </c>
-      <c r="Y2" t="str">
-        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编研究（2023）</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>主观压力值下降&gt;=1分；一周后情绪耗竭维度得分下降</v>
-      </c>
       <c r="AA2" t="str">
-        <v>连续使用3次后主观压力值未下降</v>
+        <v>家校沟通实务手册 第3章</v>
       </c>
       <c r="AB2" t="str">
-        <v>确保教师有3分钟不被打扰的环境</v>
+        <v>家长愿意继续讨论具体事实</v>
       </c>
       <c r="AC2" t="str">
-        <v>计时器、一周能量记录卡</v>
+        <v>两次尝试后情绪仍持续升级</v>
       </c>
       <c r="AD2" t="str">
-        <v>一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE2" t="str">
-        <v>HS_RX_004</v>
+        <v>记录表</v>
       </c>
       <c r="AF2" t="str">
-        <v>家校沟通合作处方库 P12</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH2" t="str">
-        <v>class_system,home_school</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>HS_RX_002</v>
       </c>
       <c r="B3" t="str">
-        <v>家访指引</v>
+        <v>事实边界记录表</v>
       </c>
       <c r="C3" t="str">
-        <v>家访指引</v>
+        <v>事实记录</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -632,46 +647,49 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>日常自我照顾和压力管理</v>
+        <v>沟通开始出现指责和归因争议时</v>
       </c>
       <c r="I3" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>家校冲突升级</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="K3" t="str">
-        <v>home_school,yellow,visit</v>
+        <v>沟通冲突升级</v>
       </c>
       <c r="L3" t="str">
-        <v>自我照顾</v>
+        <v>home_school,conflict</v>
       </c>
       <c r="M3" t="str">
-        <v>1) 记录每日能量变化 2) 识别能量消耗源 3) 制定能量补充计划</v>
+        <v>HS_ATTITUDE</v>
       </c>
       <c r="N3" t="str">
-        <v>记录本身就是一种觉察和关爱。</v>
-      </c>
-      <c r="O3" t="str">
-        <v>帮助教师建立自我照顾习惯，降低日常压力水平</v>
+        <v>把争议从情绪层面拉回可核实的事实</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">分三栏记录：家长诉求 / 已核实事实 / 待核实点
+每一条都注明时间、在场人和信息来源
+待核实点明确由谁在什么时间核实
+核实结果书面反馈给家长</v>
       </c>
       <c r="P3" t="str">
-        <v>5 分钟</v>
+        <v>这一条我需要先向任课老师核实，明天下午三点前给您答复。</v>
       </c>
       <c r="Q3" t="str">
-        <v>每日一次，持续 14 天</v>
+        <v>争议点从模糊指责收敛为可核实清单</v>
       </c>
       <c r="R3" t="str">
-        <v>14</v>
+        <v>20 分钟</v>
       </c>
       <c r="S3" t="str">
-        <v>本工具不适用于危机情境；教师处于急性心理危机时请先转介心理专员</v>
+        <v>每次冲突性沟通后</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>不要凭记忆回应；不要在未核实前认定责任</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -680,48 +698,54 @@
         <v/>
       </c>
       <c r="X3" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y3" t="str">
-        <v>教师自我效能感训练研究（2022）</v>
+        <v/>
       </c>
       <c r="Z3" t="str">
-        <v>连续一周能量记录完整且主观压力值下降</v>
+        <v>A</v>
       </c>
       <c r="AA3" t="str">
-        <v>连续3天未记录</v>
+        <v>家校沟通实务手册 第5章</v>
       </c>
       <c r="AB3" t="str">
-        <v>打印一周能量记录卡</v>
+        <v>待核实点全部有明确责任人和时限</v>
       </c>
       <c r="AC3" t="str">
-        <v>一周能量记录卡、笔</v>
+        <v>家长拒绝进入事实核实流程</v>
       </c>
       <c r="AD3" t="str">
-        <v>完成的一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE3" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF3" t="str">
-        <v>家校沟通合作处方库 P15</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>HS_RX_003</v>
       </c>
       <c r="B4" t="str">
-        <v>家校冲突调解框架</v>
+        <v>沟通容器修复计划</v>
       </c>
       <c r="C4" t="str">
-        <v>冲突调解</v>
+        <v>容器修复</v>
       </c>
       <c r="D4" t="str">
         <v>home_school</v>
@@ -736,46 +760,49 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>需要同伴支持和经验交流时</v>
+        <v>关系只在出问题时才联系，缺少正向经验</v>
       </c>
       <c r="I4" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>家校冲突升级</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="K4" t="str">
-        <v>home_school,red,conflict</v>
+        <v>关系容器不足</v>
       </c>
       <c r="L4" t="str">
-        <v>同伴支持</v>
+        <v>home_school,container</v>
       </c>
       <c r="M4" t="str">
-        <v>1) 邀请2-3位同事 2) 轮流分享当前困扰 3) 团体生成至少一条行动建议</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="N4" t="str">
-        <v>你不是一个人在战斗。</v>
-      </c>
-      <c r="O4" t="str">
-        <v>通过结构化同伴支持缓解教师的孤立感</v>
+        <v>重建可承载坦诚讨论的关系基础</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">本周主动做一次与问题无关的正向接触
+只反馈孩子的一个具体进步，不带任何请求
+两周内累计三次正向接触后，再谈需要讨论的问题
+每次接触后记录家长的回应变化</v>
       </c>
       <c r="P4" t="str">
-        <v>30 分钟</v>
+        <v>今天想跟您说件小事，孩子这周主动帮同学讲了一道题。</v>
       </c>
       <c r="Q4" t="str">
-        <v>每周一次，持续 4 周</v>
+        <v>家长回应速度和态度改善</v>
       </c>
       <c r="R4" t="str">
-        <v>28</v>
+        <v>5 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>本活动不等同于心理治疗，涉及严重心理问题时应转介专业支持</v>
+        <v>每周一次，连续三周</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>正向接触时不要夹带任何请求或批评</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -784,48 +811,54 @@
         <v/>
       </c>
       <c r="X4" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y4" t="str">
-        <v>同伴支持对教师职业倦怠干预效果研究（2021）</v>
+        <v/>
       </c>
       <c r="Z4" t="str">
-        <v>参与教师反馈压力感和孤立感下降</v>
+        <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>连续2次参与人数低于2人</v>
+        <v>家校沟通实务手册 第4章</v>
       </c>
       <c r="AB4" t="str">
-        <v>准备问题引导卡</v>
+        <v>三次接触后家长主动回应</v>
       </c>
       <c r="AC4" t="str">
-        <v>问题引导卡、白板、记号笔</v>
+        <v>三次接触后无任何回应</v>
       </c>
       <c r="AD4" t="str">
-        <v>行动建议记录表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE4" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF4" t="str">
-        <v>家校沟通合作处方库 P20</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI4" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>HS_RX_004</v>
       </c>
       <c r="B5" t="str">
-        <v>家长教育工作坊</v>
+        <v>最小请求约定法</v>
       </c>
       <c r="C5" t="str">
-        <v>家长工作坊</v>
+        <v>最小请求</v>
       </c>
       <c r="D5" t="str">
         <v>home_school</v>
@@ -840,97 +873,445 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>出现明显负面自动思维时</v>
+        <v>家长不回消息或约定的事没有落实</v>
       </c>
       <c r="I5" t="str">
+        <v>low</v>
+      </c>
+      <c r="J5" t="str">
+        <v>HS_AT_COOP</v>
+      </c>
+      <c r="K5" t="str">
+        <v>配合度不足</v>
+      </c>
+      <c r="L5" t="str">
+        <v>home_school,cooperation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>HS_COOP</v>
+      </c>
+      <c r="N5" t="str">
+        <v>把配合请求缩小到可完成的尺度</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">把原本的请求拆到一周内能完成的最小动作
+明确「做什么、什么时候、怎么反馈」三件事
+完成后当天给出正向反馈
+连续两次完成后再提高一点要求</v>
+      </c>
+      <c r="P5" t="str">
+        <v>这周只请您做一件事：晚饭后问一句今天数学课听懂了多少，周五告诉我他怎么说。</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>家长完成率提升</v>
+      </c>
+      <c r="R5" t="str">
+        <v>5 分钟</v>
+      </c>
+      <c r="S5" t="str">
+        <v>每周一次</v>
+      </c>
+      <c r="T5" t="str">
+        <v>30</v>
+      </c>
+      <c r="U5" t="str">
+        <v>不要一次提出多项请求</v>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>家校沟通实务手册 第6章</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>连续两周完成约定</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>连续两次未完成（改用 HS_RX_003）</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>HS_RX_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>定期反馈节奏表</v>
+      </c>
+      <c r="C6" t="str">
+        <v>反馈节奏</v>
+      </c>
+      <c r="D6" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="E6" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F6" t="str">
+        <v>all</v>
+      </c>
+      <c r="G6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H6" t="str">
+        <v>家长反复确认同一件事、非工作时间频繁联系</v>
+      </c>
+      <c r="I6" t="str">
         <v>medium</v>
       </c>
-      <c r="J5" t="str">
-        <v>沟通质量与信任双低</v>
-      </c>
-      <c r="K5" t="str">
-        <v>home_school,green,education</v>
-      </c>
-      <c r="L5" t="str">
-        <v>认知调整</v>
-      </c>
-      <c r="M5" t="str">
-        <v>1) 识别负面自动思维 2) 检验思维的证据 3) 生成替代性解释 4) 行动计划</v>
-      </c>
-      <c r="N5" t="str">
-        <v>想法不一定是事实，让我们一起来看看证据。</v>
-      </c>
-      <c r="O5" t="str">
-        <v>帮助教师识别和调整负面自动思维，降低认知层面的压力</v>
-      </c>
-      <c r="P5" t="str">
+      <c r="J6" t="str">
+        <v>HS_AT_ANXIETY</v>
+      </c>
+      <c r="K6" t="str">
+        <v>家长焦虑过载</v>
+      </c>
+      <c r="L6" t="str">
+        <v>home_school,anxiety</v>
+      </c>
+      <c r="M6" t="str">
+        <v>HS_ANXIETY</v>
+      </c>
+      <c r="N6" t="str">
+        <v>用可预期的信息节奏降低焦虑</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">与家长约定固定的反馈时间点，如每周五下午
+明确每次反馈包含哪三项内容
+约定非紧急事项统一在反馈时处理
+紧急情况的判断标准写清楚</v>
+      </c>
+      <c r="P6" t="str">
+        <v>我每周五下午会把这三件事同步给您，中间如果有紧急情况我会随时联系。</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>非工作时间消息量下降</v>
+      </c>
+      <c r="R6" t="str">
         <v>15 分钟</v>
       </c>
-      <c r="Q5" t="str">
-        <v>每周 2-3 次，持续 4 周</v>
-      </c>
-      <c r="R5" t="str">
-        <v>14</v>
-      </c>
-      <c r="S5" t="str">
-        <v>有严重抑郁症状的教师应先在心理专员指导下使用</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
+      <c r="S6" t="str">
+        <v>约定一次，长期执行</v>
+      </c>
+      <c r="T6" t="str">
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <v>不要承诺随时回复；约定后必须自己先遵守</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
         <v>B</v>
       </c>
-      <c r="Y5" t="str">
-        <v>Beck 认知疗法教师适应性改编研究（2022）</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2周后负面自动思维频率下降 &gt;=30%</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>使用2周后负面思维频率未下降且教师反馈无改善</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>打印认知重构工作表</v>
-      </c>
-      <c r="AC5" t="str">
-        <v>认知重构工作表、笔</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>完成的认知重构工作表</v>
-      </c>
-      <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
-        <v>家校沟通合作处方库 P18</v>
-      </c>
-      <c r="AG5" t="str">
+      <c r="AA6" t="str">
+        <v>家校沟通实务手册 第7章</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>非工作时间消息减少 50%</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>约定后一周内仍频繁越界</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI6" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH5" t="str">
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>HS_RX_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>承诺兑现清单</v>
+      </c>
+      <c r="C7" t="str">
+        <v>承诺兑现</v>
+      </c>
+      <c r="D7" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="E7" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F7" t="str">
+        <v>all</v>
+      </c>
+      <c r="G7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H7" t="str">
+        <v>家长不相信教师站在孩子一边</v>
+      </c>
+      <c r="I7" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J7" t="str">
+        <v>HS_AT_TRUST</v>
+      </c>
+      <c r="K7" t="str">
+        <v>信任基础薄弱</v>
+      </c>
+      <c r="L7" t="str">
+        <v>home_school,trust</v>
+      </c>
+      <c r="M7" t="str">
+        <v>HS_TRUST</v>
+      </c>
+      <c r="N7" t="str">
+        <v>用可验证的行为重建信任</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">只承诺一件本周确定能做到的小事
+明确完成时间和验证方式
+按时完成并主动告知结果
+连续兑现三次后再讨论更大的议题</v>
+      </c>
+      <c r="P7" t="str">
+        <v>这周我会安排他坐到第二排，周五我告诉您效果怎么样。</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>家长开始接受教师的专业判断</v>
+      </c>
+      <c r="R7" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S7" t="str">
+        <v>每周一次，连续三周</v>
+      </c>
+      <c r="T7" t="str">
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <v>不要承诺不在自己权限内的事</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>家校信任重建研究</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>连续三次按时兑现</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>任一次未按时兑现（需重新开始）</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>HS_RX_007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>E 级保护通道操作卡</v>
+      </c>
+      <c r="C8" t="str">
+        <v>E级保护</v>
+      </c>
+      <c r="D8" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="E8" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F8" t="str">
+        <v>all</v>
+      </c>
+      <c r="G8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H8" t="str">
+        <v>家长出现威胁、公开抹黑或恶意维权</v>
+      </c>
+      <c r="I8" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J8" t="str">
+        <v>HS_AT_CONFLICT</v>
+      </c>
+      <c r="K8" t="str">
+        <v>沟通冲突升级</v>
+      </c>
+      <c r="L8" t="str">
+        <v>home_school,conflict,crisis</v>
+      </c>
+      <c r="M8" t="str">
+        <v>HS_ATTITUDE</v>
+      </c>
+      <c r="N8" t="str">
+        <v>保护教师并把处置转到学校层面</v>
+      </c>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">立即停止单独沟通，不再单方回应
+完整保存聊天记录、通话记录和相关材料
+当天上报年级组长并填写事件说明
+后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+      </c>
+      <c r="P8" t="str">
+        <v>这件事我需要请年级组长一起来处理，我们另约时间当面谈。</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>教师退出单独沟通，风险转由学校承接</v>
+      </c>
+      <c r="R8" t="str">
+        <v>30 分钟</v>
+      </c>
+      <c r="S8" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T8" t="str">
+        <v>30</v>
+      </c>
+      <c r="U8" t="str">
+        <v>严禁教师单独回应威胁；严禁删除任何沟通记录</v>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>校方家校冲突处置规范</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>24 小时内完成上报和留痕</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>教师仍在单独沟通</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ8" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -972,28 +1353,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境</v>
+        <v>先复述家长的担心，用他的</v>
       </c>
       <c r="D2" t="str">
-        <v>暂时离开当前工作环境（办公室、教室），找到一个安静不被打扰的空间</v>
+        <v>先复述家长的担心，用他的原话</v>
       </c>
       <c r="E2" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>不需要走很远，去走廊尽头或空会议室即可</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>我能感受到您现在很担心。我们先把事实逐项核实，再一起决定下一步。</v>
       </c>
       <c r="I2" t="str">
-        <v>教师已经离开原环境，至少获得3分钟不被干扰的时间</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J2" t="str">
-        <v>如果实在无法离开怎么办？（答：至少转身背对工作区域，闭眼30秒）</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1004,28 +1385,28 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>三轮缓慢呼吸</v>
+        <v>表达理解而非认同：「我能</v>
       </c>
       <c r="D3" t="str">
-        <v>进行三轮缓慢深呼吸：吸气4秒→屏息2秒→呼气6秒。每轮之间自然呼吸10秒</v>
+        <v>表达理解而非认同：「我能感受到您现在很担心」</v>
       </c>
       <c r="E3" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>计时器（可选）</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>不要刻意用力呼吸，重点是让呼气比吸气更长</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成了三轮呼吸</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J3" t="str">
-        <v>如果注意力无法集中怎么办？（答：把注意力放在呼气的感觉上，每次走神都重新回来即可）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1036,25 +1417,25 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>命名此刻的情绪</v>
+        <v>把话题引向可核实的事实</v>
       </c>
       <c r="D4" t="str">
-        <v>问自己「我现在感受到的是什么？」——是愤怒、委屈、无力、焦虑、还是别的？给情绪一个名字</v>
+        <v>把话题引向可核实的事实</v>
       </c>
       <c r="E4" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>不需要分析原因，只需要命名。如果同时有多种情绪，选最强烈的那一个</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>教师能够说出至少一种情绪的名称</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1068,25 +1449,25 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个最小行动</v>
+        <v>约定一个具体的下一步和反</v>
       </c>
       <c r="D5" t="str">
-        <v>问自己「接下来5分钟，我能做的最小、最简单的一件事是什么？」选一件，然后做</v>
+        <v>约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="E5" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>最小行动的标准：不需要别人配合，不需要准备，立即能做</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>教师选出了至少一个可行的最小行动</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1100,25 +1481,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>记录今日能量</v>
+        <v>分三栏记录：家长诉求 /</v>
       </c>
       <c r="D6" t="str">
-        <v>在能量记录卡上记录你今天几个关键时间点的能量状态（1-10分）</v>
+        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点</v>
       </c>
       <c r="E6" t="str">
-        <v>3分钟</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>能量记录卡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>保持诚实，不需要美化</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>这一条我需要先向任课老师核实，明天下午三点前给您答复。</v>
       </c>
       <c r="I6" t="str">
-        <v>完成了至少3个时间点的记录</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1132,40 +1513,744 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>识别能量消耗</v>
+        <v>每一条都注明时间、在场人</v>
       </c>
       <c r="D7" t="str">
-        <v>回顾今天的能量低谷，思考是什么消耗了你的能量</v>
+        <v>每一条都注明时间、在场人和信息来源</v>
       </c>
       <c r="E7" t="str">
-        <v>2分钟</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>不需要找出所有原因，选影响最大的1-2个即可</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>识别出至少1个能量消耗源</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_RX_002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>待核实点明确由谁在什么时</v>
+      </c>
+      <c r="D8" t="str">
+        <v>待核实点明确由谁在什么时间核实</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HS_RX_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>核实结果书面反馈给家长</v>
+      </c>
+      <c r="D9" t="str">
+        <v>核实结果书面反馈给家长</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HS_RX_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>本周主动做一次与问题无关</v>
+      </c>
+      <c r="D10" t="str">
+        <v>本周主动做一次与问题无关的正向接触</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H10" t="str">
+        <v>今天想跟您说件小事，孩子这周主动帮同学讲了一道题。</v>
+      </c>
+      <c r="I10" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HS_RX_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>只反馈孩子的一个具体进步</v>
+      </c>
+      <c r="D11" t="str">
+        <v>只反馈孩子的一个具体进步，不带任何请求</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HS_RX_003</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>两周内累计三次正向接触后</v>
+      </c>
+      <c r="D12" t="str">
+        <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HS_RX_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>每次接触后记录家长的回应</v>
+      </c>
+      <c r="D13" t="str">
+        <v>每次接触后记录家长的回应变化</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HS_RX_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>把原本的请求拆到一周内能</v>
+      </c>
+      <c r="D14" t="str">
+        <v>把原本的请求拆到一周内能完成的最小动作</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H14" t="str">
+        <v>这周只请您做一件事：晚饭后问一句今天数学课听懂了多少，周五告诉我他怎么说。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HS_RX_004</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>明确「做什么、什么时候、</v>
+      </c>
+      <c r="D15" t="str">
+        <v>明确「做什么、什么时候、怎么反馈」三件事</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HS_RX_004</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>完成后当天给出正向反馈</v>
+      </c>
+      <c r="D16" t="str">
+        <v>完成后当天给出正向反馈</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HS_RX_004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>连续两次完成后再提高一点</v>
+      </c>
+      <c r="D17" t="str">
+        <v>连续两次完成后再提高一点要求</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HS_RX_005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>与家长约定固定的反馈时间</v>
+      </c>
+      <c r="D18" t="str">
+        <v>与家长约定固定的反馈时间点，如每周五下午</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H18" t="str">
+        <v>我每周五下午会把这三件事同步给您，中间如果有紧急情况我会随时联系。</v>
+      </c>
+      <c r="I18" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HS_RX_005</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>明确每次反馈包含哪三项内</v>
+      </c>
+      <c r="D19" t="str">
+        <v>明确每次反馈包含哪三项内容</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HS_RX_005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>约定非紧急事项统一在反馈</v>
+      </c>
+      <c r="D20" t="str">
+        <v>约定非紧急事项统一在反馈时处理</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HS_RX_005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>紧急情况的判断标准写清楚</v>
+      </c>
+      <c r="D21" t="str">
+        <v>紧急情况的判断标准写清楚</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HS_RX_006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>只承诺一件本周确定能做到</v>
+      </c>
+      <c r="D22" t="str">
+        <v>只承诺一件本周确定能做到的小事</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H22" t="str">
+        <v>这周我会安排他坐到第二排，周五我告诉您效果怎么样。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HS_RX_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>明确完成时间和验证方式</v>
+      </c>
+      <c r="D23" t="str">
+        <v>明确完成时间和验证方式</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HS_RX_006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>按时完成并主动告知结果</v>
+      </c>
+      <c r="D24" t="str">
+        <v>按时完成并主动告知结果</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HS_RX_006</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>连续兑现三次后再讨论更大</v>
+      </c>
+      <c r="D25" t="str">
+        <v>连续兑现三次后再讨论更大的议题</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HS_RX_007</v>
+      </c>
+      <c r="B26" t="str">
+        <v>1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>立即停止单独沟通，不再单</v>
+      </c>
+      <c r="D26" t="str">
+        <v>立即停止单独沟通，不再单方回应</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H26" t="str">
+        <v>这件事我需要请年级组长一起来处理，我们另约时间当面谈。</v>
+      </c>
+      <c r="I26" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HS_RX_007</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2</v>
+      </c>
+      <c r="C27" t="str">
+        <v>完整保存聊天记录、通话记</v>
+      </c>
+      <c r="D27" t="str">
+        <v>完整保存聊天记录、通话记录和相关材料</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HS_RX_007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>当天上报年级组长并填写事</v>
+      </c>
+      <c r="D28" t="str">
+        <v>当天上报年级组长并填写事件说明</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HS_RX_007</v>
+      </c>
+      <c r="B29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>后续沟通全部由年级组长或</v>
+      </c>
+      <c r="D29" t="str">
+        <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1192,76 +2277,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B2" t="str">
-        <v>教师自评抑郁量表得分&gt;=15</v>
+        <v>事件已进入法律程序</v>
       </c>
       <c r="C2" t="str">
         <v>block</v>
       </c>
       <c r="D2" t="str">
-        <v>抑郁风险较高时应先进行专业心理评估，不可单独依赖呼吸练习</v>
+        <v>进入法律程序后一切沟通由校方法务承接</v>
       </c>
       <c r="E2" t="str">
-        <v>通知心理专员进行评估</v>
+        <v>移交校方法务处理</v>
       </c>
       <c r="F2" t="str">
-        <v>存在抑郁风险的教师</v>
+        <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>HS_RX_004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>教师处于急性危机状态</v>
-      </c>
-      <c r="C3" t="str">
-        <v>block</v>
-      </c>
-      <c r="D3" t="str">
-        <v>急性危机时认知重构类工具可能加重混乱感</v>
-      </c>
-      <c r="E3" t="str">
-        <v>先使用安全稳定化工具，等状态稳定后再使用</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>HS_RX_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>参与教师超过8人</v>
-      </c>
-      <c r="C4" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>超过8人时小组讨论深度下降，建议拆分小组</v>
-      </c>
-      <c r="E4" t="str">
-        <v>每组控制在4-6人，增加一名引导员</v>
-      </c>
-      <c r="F4" t="str">
-        <v>年级组长</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>家校沟通合作手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/tool.xlsx
+++ b/business-libraries/test-data/home_school/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>先跟后带话术卡</v>
       </c>
       <c r="C2" t="str">
-        <v>先跟后带</v>
+        <v>先跟后带话术卡</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -540,25 +540,22 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="K2" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界不足</v>
       </c>
       <c r="L2" t="str">
         <v>home_school,container</v>
       </c>
       <c r="M2" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D3</v>
       </c>
       <c r="N2" t="str">
         <v>在不认同内容的前提下承接情绪</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">先复述家长的担心，用他的原话
-表达理解而非认同：「我能感受到您现在很担心」
-把话题引向可核实的事实
-约定一个具体的下一步和反馈时间</v>
+      <c r="O2" t="str">
+        <v>先复述家长的担心，用他的原话；表达理解而非认同：「我能感受到您现在很担心」；把话题引向可核实的事实；约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="P2" t="str">
         <v>我能感受到您现在很担心。我们先把事实逐项核实，再一起决定下一步。</v>
@@ -618,21 +615,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>事实边界记录表</v>
       </c>
       <c r="C3" t="str">
-        <v>事实记录</v>
+        <v>事实边界记录表</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -653,7 +650,7 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="K3" t="str">
         <v>沟通冲突升级</v>
@@ -662,16 +659,13 @@
         <v>home_school,conflict</v>
       </c>
       <c r="M3" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D4</v>
       </c>
       <c r="N3" t="str">
         <v>把争议从情绪层面拉回可核实的事实</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">分三栏记录：家长诉求 / 已核实事实 / 待核实点
-每一条都注明时间、在场人和信息来源
-待核实点明确由谁在什么时间核实
-核实结果书面反馈给家长</v>
+      <c r="O3" t="str">
+        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点；每一条都注明时间、在场人和信息来源；待核实点明确由谁在什么时间核实；核实结果书面反馈给家长</v>
       </c>
       <c r="P3" t="str">
         <v>这一条我需要先向任课老师核实，明天下午三点前给您答复。</v>
@@ -731,21 +725,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>沟通容器修复计划</v>
       </c>
       <c r="C4" t="str">
-        <v>容器修复</v>
+        <v>沟通容器修复计划</v>
       </c>
       <c r="D4" t="str">
         <v>home_school</v>
@@ -766,25 +760,22 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="K4" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界不足</v>
       </c>
       <c r="L4" t="str">
         <v>home_school,container</v>
       </c>
       <c r="M4" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D3</v>
       </c>
       <c r="N4" t="str">
         <v>重建可承载坦诚讨论的关系基础</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">本周主动做一次与问题无关的正向接触
-只反馈孩子的一个具体进步，不带任何请求
-两周内累计三次正向接触后，再谈需要讨论的问题
-每次接触后记录家长的回应变化</v>
+      <c r="O4" t="str">
+        <v>本周主动做一次与问题无关的正向接触；只反馈孩子的一个具体进步，不带任何请求；两周内累计三次正向接触后，再谈需要讨论的问题；每次接触后记录家长的回应变化</v>
       </c>
       <c r="P4" t="str">
         <v>今天想跟您说件小事，孩子这周主动帮同学讲了一道题。</v>
@@ -844,21 +835,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>最小请求约定法</v>
       </c>
       <c r="C5" t="str">
-        <v>最小请求</v>
+        <v>最小请求约定法</v>
       </c>
       <c r="D5" t="str">
         <v>home_school</v>
@@ -879,25 +870,22 @@
         <v>low</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_03</v>
       </c>
       <c r="K5" t="str">
-        <v>配合度不足</v>
+        <v>参与效能不足</v>
       </c>
       <c r="L5" t="str">
         <v>home_school,cooperation</v>
       </c>
       <c r="M5" t="str">
-        <v>HS_COOP</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="N5" t="str">
         <v>把配合请求缩小到可完成的尺度</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">把原本的请求拆到一周内能完成的最小动作
-明确「做什么、什么时候、怎么反馈」三件事
-完成后当天给出正向反馈
-连续两次完成后再提高一点要求</v>
+      <c r="O5" t="str">
+        <v>把原本的请求拆到一周内能完成的最小动作；明确「做什么、什么时候、怎么反馈」三件事；完成后当天给出正向反馈；连续两次完成后再提高一点要求</v>
       </c>
       <c r="P5" t="str">
         <v>这周只请您做一件事：晚饭后问一句今天数学课听懂了多少，周五告诉我他怎么说。</v>
@@ -957,21 +945,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>定期反馈节奏表</v>
       </c>
       <c r="C6" t="str">
-        <v>反馈节奏</v>
+        <v>定期反馈节奏表</v>
       </c>
       <c r="D6" t="str">
         <v>home_school</v>
@@ -992,7 +980,7 @@
         <v>medium</v>
       </c>
       <c r="J6" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="K6" t="str">
         <v>家长焦虑过载</v>
@@ -1001,16 +989,13 @@
         <v>home_school,anxiety</v>
       </c>
       <c r="M6" t="str">
-        <v>HS_ANXIETY</v>
+        <v>HS_S2D1</v>
       </c>
       <c r="N6" t="str">
         <v>用可预期的信息节奏降低焦虑</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">与家长约定固定的反馈时间点，如每周五下午
-明确每次反馈包含哪三项内容
-约定非紧急事项统一在反馈时处理
-紧急情况的判断标准写清楚</v>
+      <c r="O6" t="str">
+        <v>与家长约定固定的反馈时间点，如每周五下午；明确每次反馈包含哪三项内容；约定非紧急事项统一在反馈时处理；紧急情况的判断标准写清楚</v>
       </c>
       <c r="P6" t="str">
         <v>我每周五下午会把这三件事同步给您，中间如果有紧急情况我会随时联系。</v>
@@ -1070,21 +1055,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>承诺兑现清单</v>
       </c>
       <c r="C7" t="str">
-        <v>承诺兑现</v>
+        <v>承诺兑现清单</v>
       </c>
       <c r="D7" t="str">
         <v>home_school</v>
@@ -1105,25 +1090,22 @@
         <v>medium</v>
       </c>
       <c r="J7" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="K7" t="str">
-        <v>信任基础薄弱</v>
+        <v>信任关系薄弱</v>
       </c>
       <c r="L7" t="str">
         <v>home_school,trust</v>
       </c>
       <c r="M7" t="str">
-        <v>HS_TRUST</v>
+        <v>HS_S2D3</v>
       </c>
       <c r="N7" t="str">
         <v>用可验证的行为重建信任</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">只承诺一件本周确定能做到的小事
-明确完成时间和验证方式
-按时完成并主动告知结果
-连续兑现三次后再讨论更大的议题</v>
+      <c r="O7" t="str">
+        <v>只承诺一件本周确定能做到的小事；明确完成时间和验证方式；按时完成并主动告知结果；连续兑现三次后再讨论更大的议题</v>
       </c>
       <c r="P7" t="str">
         <v>这周我会安排他坐到第二排，周五我告诉您效果怎么样。</v>
@@ -1183,21 +1165,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B8" t="str">
         <v>E 级保护通道操作卡</v>
       </c>
       <c r="C8" t="str">
-        <v>E级保护</v>
+        <v>E 级保护通道操</v>
       </c>
       <c r="D8" t="str">
         <v>home_school</v>
@@ -1218,25 +1200,22 @@
         <v>crisis</v>
       </c>
       <c r="J8" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="K8" t="str">
         <v>沟通冲突升级</v>
       </c>
       <c r="L8" t="str">
-        <v>home_school,conflict,crisis</v>
+        <v>home_school,conflict</v>
       </c>
       <c r="M8" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D4</v>
       </c>
       <c r="N8" t="str">
         <v>保护教师并把处置转到学校层面</v>
       </c>
-      <c r="O8" t="str" xml:space="preserve">
-        <v xml:space="preserve">立即停止单独沟通，不再单方回应
-完整保存聊天记录、通话记录和相关材料
-当天上报年级组长并填写事件说明
-后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+      <c r="O8" t="str">
+        <v>立即停止单独沟通，不再单方回应；完整保存聊天记录、通话记录和相关材料；当天上报年级组长并填写事件说明；后续沟通全部由年级组长或校方主导，教师只提供事实</v>
       </c>
       <c r="P8" t="str">
         <v>这件事我需要请年级组长一起来处理，我们另约时间当面谈。</v>
@@ -1296,7 +1275,7 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI8" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -1347,13 +1326,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>先复述家长的担心，用他的</v>
+        <v>先复述家长的担心，用他的原话</v>
       </c>
       <c r="D2" t="str">
         <v>先复述家长的担心，用他的原话</v>
@@ -1379,13 +1358,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>表达理解而非认同：「我能</v>
+        <v>表达理解而非认同：「我能感受到您现在很担心」</v>
       </c>
       <c r="D3" t="str">
         <v>表达理解而非认同：「我能感受到您现在很担心」</v>
@@ -1411,7 +1390,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
@@ -1443,13 +1422,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>约定一个具体的下一步和反</v>
+        <v>约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="D5" t="str">
         <v>约定一个具体的下一步和反馈时间</v>
@@ -1475,13 +1454,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>分三栏记录：家长诉求 /</v>
+        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实</v>
       </c>
       <c r="D6" t="str">
         <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点</v>
@@ -1507,13 +1486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>每一条都注明时间、在场人</v>
+        <v>每一条都注明时间、在场人和信息来源</v>
       </c>
       <c r="D7" t="str">
         <v>每一条都注明时间、在场人和信息来源</v>
@@ -1539,13 +1518,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>待核实点明确由谁在什么时</v>
+        <v>待核实点明确由谁在什么时间核实</v>
       </c>
       <c r="D8" t="str">
         <v>待核实点明确由谁在什么时间核实</v>
@@ -1571,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
@@ -1603,13 +1582,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>本周主动做一次与问题无关</v>
+        <v>本周主动做一次与问题无关的正向接触</v>
       </c>
       <c r="D10" t="str">
         <v>本周主动做一次与问题无关的正向接触</v>
@@ -1635,13 +1614,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>只反馈孩子的一个具体进步</v>
+        <v>只反馈孩子的一个具体进步，不带任何请求</v>
       </c>
       <c r="D11" t="str">
         <v>只反馈孩子的一个具体进步，不带任何请求</v>
@@ -1667,13 +1646,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>两周内累计三次正向接触后</v>
+        <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
       </c>
       <c r="D12" t="str">
         <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
@@ -1699,13 +1678,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>每次接触后记录家长的回应</v>
+        <v>每次接触后记录家长的回应变化</v>
       </c>
       <c r="D13" t="str">
         <v>每次接触后记录家长的回应变化</v>
@@ -1731,13 +1710,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>把原本的请求拆到一周内能</v>
+        <v>把原本的请求拆到一周内能完成的最小动作</v>
       </c>
       <c r="D14" t="str">
         <v>把原本的请求拆到一周内能完成的最小动作</v>
@@ -1763,13 +1742,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>明确「做什么、什么时候、</v>
+        <v>明确「做什么、什么时候、怎么反馈」三件事</v>
       </c>
       <c r="D15" t="str">
         <v>明确「做什么、什么时候、怎么反馈」三件事</v>
@@ -1795,7 +1774,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
@@ -1827,13 +1806,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>连续两次完成后再提高一点</v>
+        <v>连续两次完成后再提高一点要求</v>
       </c>
       <c r="D17" t="str">
         <v>连续两次完成后再提高一点要求</v>
@@ -1859,13 +1838,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>与家长约定固定的反馈时间</v>
+        <v>与家长约定固定的反馈时间点，如每周五下午</v>
       </c>
       <c r="D18" t="str">
         <v>与家长约定固定的反馈时间点，如每周五下午</v>
@@ -1891,13 +1870,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>明确每次反馈包含哪三项内</v>
+        <v>明确每次反馈包含哪三项内容</v>
       </c>
       <c r="D19" t="str">
         <v>明确每次反馈包含哪三项内容</v>
@@ -1923,13 +1902,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>约定非紧急事项统一在反馈</v>
+        <v>约定非紧急事项统一在反馈时处理</v>
       </c>
       <c r="D20" t="str">
         <v>约定非紧急事项统一在反馈时处理</v>
@@ -1955,7 +1934,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
@@ -1987,13 +1966,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>只承诺一件本周确定能做到</v>
+        <v>只承诺一件本周确定能做到的小事</v>
       </c>
       <c r="D22" t="str">
         <v>只承诺一件本周确定能做到的小事</v>
@@ -2019,7 +1998,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
@@ -2051,7 +2030,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
@@ -2083,13 +2062,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>连续兑现三次后再讨论更大</v>
+        <v>连续兑现三次后再讨论更大的议题</v>
       </c>
       <c r="D25" t="str">
         <v>连续兑现三次后再讨论更大的议题</v>
@@ -2115,13 +2094,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B26" t="str">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>立即停止单独沟通，不再单</v>
+        <v>立即停止单独沟通，不再单方回应</v>
       </c>
       <c r="D26" t="str">
         <v>立即停止单独沟通，不再单方回应</v>
@@ -2147,13 +2126,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B27" t="str">
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>完整保存聊天记录、通话记</v>
+        <v>完整保存聊天记录、通话记录和相关材料</v>
       </c>
       <c r="D27" t="str">
         <v>完整保存聊天记录、通话记录和相关材料</v>
@@ -2179,13 +2158,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B28" t="str">
         <v>3</v>
       </c>
       <c r="C28" t="str">
-        <v>当天上报年级组长并填写事</v>
+        <v>当天上报年级组长并填写事件说明</v>
       </c>
       <c r="D28" t="str">
         <v>当天上报年级组长并填写事件说明</v>
@@ -2211,13 +2190,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B29" t="str">
         <v>4</v>
       </c>
       <c r="C29" t="str">
-        <v>后续沟通全部由年级组长或</v>
+        <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
       </c>
       <c r="D29" t="str">
         <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
@@ -2277,7 +2256,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B2" t="str">
         <v>事件已进入法律程序</v>

--- a/business-libraries/test-data/home_school/tool.xlsx
+++ b/business-libraries/test-data/home_school/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>HS_RX_01</v>
+        <v>HS_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>先跟后带话术卡</v>
       </c>
       <c r="C2" t="str">
-        <v>先跟后带话术卡</v>
+        <v>先跟后带</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -540,22 +540,25 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_AT_02</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="K2" t="str">
-        <v>角色边界不足</v>
+        <v>关系容器不足</v>
       </c>
       <c r="L2" t="str">
         <v>home_school,container</v>
       </c>
       <c r="M2" t="str">
-        <v>HS_S1D3</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="N2" t="str">
         <v>在不认同内容的前提下承接情绪</v>
       </c>
-      <c r="O2" t="str">
-        <v>先复述家长的担心，用他的原话；表达理解而非认同：「我能感受到您现在很担心」；把话题引向可核实的事实；约定一个具体的下一步和反馈时间</v>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">先复述家长的担心，用他的原话
+表达理解而非认同：「我能感受到您现在很担心」
+把话题引向可核实的事实
+约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="P2" t="str">
         <v>我能感受到您现在很担心。我们先把事实逐项核实，再一起决定下一步。</v>
@@ -615,21 +618,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>HS_RX_02</v>
+        <v>HS_RX_002</v>
       </c>
       <c r="B3" t="str">
         <v>事实边界记录表</v>
       </c>
       <c r="C3" t="str">
-        <v>事实边界记录表</v>
+        <v>事实记录</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -650,7 +653,7 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="K3" t="str">
         <v>沟通冲突升级</v>
@@ -659,13 +662,16 @@
         <v>home_school,conflict</v>
       </c>
       <c r="M3" t="str">
-        <v>HS_S1D4</v>
+        <v>HS_ATTITUDE</v>
       </c>
       <c r="N3" t="str">
         <v>把争议从情绪层面拉回可核实的事实</v>
       </c>
-      <c r="O3" t="str">
-        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点；每一条都注明时间、在场人和信息来源；待核实点明确由谁在什么时间核实；核实结果书面反馈给家长</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">分三栏记录：家长诉求 / 已核实事实 / 待核实点
+每一条都注明时间、在场人和信息来源
+待核实点明确由谁在什么时间核实
+核实结果书面反馈给家长</v>
       </c>
       <c r="P3" t="str">
         <v>这一条我需要先向任课老师核实，明天下午三点前给您答复。</v>
@@ -725,21 +731,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>HS_RX_03</v>
+        <v>HS_RX_003</v>
       </c>
       <c r="B4" t="str">
         <v>沟通容器修复计划</v>
       </c>
       <c r="C4" t="str">
-        <v>沟通容器修复计划</v>
+        <v>容器修复</v>
       </c>
       <c r="D4" t="str">
         <v>home_school</v>
@@ -760,22 +766,25 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_AT_02</v>
+        <v>HS_AT_CONTAINER</v>
       </c>
       <c r="K4" t="str">
-        <v>角色边界不足</v>
+        <v>关系容器不足</v>
       </c>
       <c r="L4" t="str">
         <v>home_school,container</v>
       </c>
       <c r="M4" t="str">
-        <v>HS_S1D3</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="N4" t="str">
         <v>重建可承载坦诚讨论的关系基础</v>
       </c>
-      <c r="O4" t="str">
-        <v>本周主动做一次与问题无关的正向接触；只反馈孩子的一个具体进步，不带任何请求；两周内累计三次正向接触后，再谈需要讨论的问题；每次接触后记录家长的回应变化</v>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">本周主动做一次与问题无关的正向接触
+只反馈孩子的一个具体进步，不带任何请求
+两周内累计三次正向接触后，再谈需要讨论的问题
+每次接触后记录家长的回应变化</v>
       </c>
       <c r="P4" t="str">
         <v>今天想跟您说件小事，孩子这周主动帮同学讲了一道题。</v>
@@ -835,21 +844,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="B5" t="str">
         <v>最小请求约定法</v>
       </c>
       <c r="C5" t="str">
-        <v>最小请求约定法</v>
+        <v>最小请求</v>
       </c>
       <c r="D5" t="str">
         <v>home_school</v>
@@ -870,22 +879,25 @@
         <v>low</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_AT_03</v>
+        <v>HS_AT_COOP</v>
       </c>
       <c r="K5" t="str">
-        <v>参与效能不足</v>
+        <v>配合度不足</v>
       </c>
       <c r="L5" t="str">
         <v>home_school,cooperation</v>
       </c>
       <c r="M5" t="str">
-        <v>HS_S1D1</v>
+        <v>HS_COOP</v>
       </c>
       <c r="N5" t="str">
         <v>把配合请求缩小到可完成的尺度</v>
       </c>
-      <c r="O5" t="str">
-        <v>把原本的请求拆到一周内能完成的最小动作；明确「做什么、什么时候、怎么反馈」三件事；完成后当天给出正向反馈；连续两次完成后再提高一点要求</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">把原本的请求拆到一周内能完成的最小动作
+明确「做什么、什么时候、怎么反馈」三件事
+完成后当天给出正向反馈
+连续两次完成后再提高一点要求</v>
       </c>
       <c r="P5" t="str">
         <v>这周只请您做一件事：晚饭后问一句今天数学课听懂了多少，周五告诉我他怎么说。</v>
@@ -945,21 +957,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="B6" t="str">
         <v>定期反馈节奏表</v>
       </c>
       <c r="C6" t="str">
-        <v>定期反馈节奏表</v>
+        <v>反馈节奏</v>
       </c>
       <c r="D6" t="str">
         <v>home_school</v>
@@ -980,7 +992,7 @@
         <v>medium</v>
       </c>
       <c r="J6" t="str">
-        <v>HS_AT_04</v>
+        <v>HS_AT_ANXIETY</v>
       </c>
       <c r="K6" t="str">
         <v>家长焦虑过载</v>
@@ -989,13 +1001,16 @@
         <v>home_school,anxiety</v>
       </c>
       <c r="M6" t="str">
-        <v>HS_S2D1</v>
+        <v>HS_ANXIETY</v>
       </c>
       <c r="N6" t="str">
         <v>用可预期的信息节奏降低焦虑</v>
       </c>
-      <c r="O6" t="str">
-        <v>与家长约定固定的反馈时间点，如每周五下午；明确每次反馈包含哪三项内容；约定非紧急事项统一在反馈时处理；紧急情况的判断标准写清楚</v>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">与家长约定固定的反馈时间点，如每周五下午
+明确每次反馈包含哪三项内容
+约定非紧急事项统一在反馈时处理
+紧急情况的判断标准写清楚</v>
       </c>
       <c r="P6" t="str">
         <v>我每周五下午会把这三件事同步给您，中间如果有紧急情况我会随时联系。</v>
@@ -1055,21 +1070,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="B7" t="str">
         <v>承诺兑现清单</v>
       </c>
       <c r="C7" t="str">
-        <v>承诺兑现清单</v>
+        <v>承诺兑现</v>
       </c>
       <c r="D7" t="str">
         <v>home_school</v>
@@ -1090,22 +1105,25 @@
         <v>medium</v>
       </c>
       <c r="J7" t="str">
-        <v>HS_AT_05</v>
+        <v>HS_AT_TRUST</v>
       </c>
       <c r="K7" t="str">
-        <v>信任关系薄弱</v>
+        <v>信任基础薄弱</v>
       </c>
       <c r="L7" t="str">
         <v>home_school,trust</v>
       </c>
       <c r="M7" t="str">
-        <v>HS_S2D3</v>
+        <v>HS_TRUST</v>
       </c>
       <c r="N7" t="str">
         <v>用可验证的行为重建信任</v>
       </c>
-      <c r="O7" t="str">
-        <v>只承诺一件本周确定能做到的小事；明确完成时间和验证方式；按时完成并主动告知结果；连续兑现三次后再讨论更大的议题</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">只承诺一件本周确定能做到的小事
+明确完成时间和验证方式
+按时完成并主动告知结果
+连续兑现三次后再讨论更大的议题</v>
       </c>
       <c r="P7" t="str">
         <v>这周我会安排他坐到第二排，周五我告诉您效果怎么样。</v>
@@ -1165,21 +1183,21 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B8" t="str">
         <v>E 级保护通道操作卡</v>
       </c>
       <c r="C8" t="str">
-        <v>E 级保护通道操</v>
+        <v>E级保护</v>
       </c>
       <c r="D8" t="str">
         <v>home_school</v>
@@ -1200,22 +1218,25 @@
         <v>crisis</v>
       </c>
       <c r="J8" t="str">
-        <v>HS_AT_01</v>
+        <v>HS_AT_CONFLICT</v>
       </c>
       <c r="K8" t="str">
         <v>沟通冲突升级</v>
       </c>
       <c r="L8" t="str">
-        <v>home_school,conflict</v>
+        <v>home_school,conflict,crisis</v>
       </c>
       <c r="M8" t="str">
-        <v>HS_S1D4</v>
+        <v>HS_ATTITUDE</v>
       </c>
       <c r="N8" t="str">
         <v>保护教师并把处置转到学校层面</v>
       </c>
-      <c r="O8" t="str">
-        <v>立即停止单独沟通，不再单方回应；完整保存聊天记录、通话记录和相关材料；当天上报年级组长并填写事件说明；后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">立即停止单独沟通，不再单方回应
+完整保存聊天记录、通话记录和相关材料
+当天上报年级组长并填写事件说明
+后续沟通全部由年级组长或校方主导，教师只提供事实</v>
       </c>
       <c r="P8" t="str">
         <v>这件事我需要请年级组长一起来处理，我们另约时间当面谈。</v>
@@ -1275,7 +1296,7 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AI8" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -1326,13 +1347,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_01</v>
+        <v>HS_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>先复述家长的担心，用他的原话</v>
+        <v>先复述家长的担心，用他的</v>
       </c>
       <c r="D2" t="str">
         <v>先复述家长的担心，用他的原话</v>
@@ -1358,13 +1379,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_RX_01</v>
+        <v>HS_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>表达理解而非认同：「我能感受到您现在很担心」</v>
+        <v>表达理解而非认同：「我能</v>
       </c>
       <c r="D3" t="str">
         <v>表达理解而非认同：「我能感受到您现在很担心」</v>
@@ -1390,7 +1411,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_RX_01</v>
+        <v>HS_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
@@ -1422,13 +1443,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_RX_01</v>
+        <v>HS_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>约定一个具体的下一步和反馈时间</v>
+        <v>约定一个具体的下一步和反</v>
       </c>
       <c r="D5" t="str">
         <v>约定一个具体的下一步和反馈时间</v>
@@ -1454,13 +1475,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_RX_02</v>
+        <v>HS_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实</v>
+        <v>分三栏记录：家长诉求 /</v>
       </c>
       <c r="D6" t="str">
         <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点</v>
@@ -1486,13 +1507,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_RX_02</v>
+        <v>HS_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>每一条都注明时间、在场人和信息来源</v>
+        <v>每一条都注明时间、在场人</v>
       </c>
       <c r="D7" t="str">
         <v>每一条都注明时间、在场人和信息来源</v>
@@ -1518,13 +1539,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_RX_02</v>
+        <v>HS_RX_002</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>待核实点明确由谁在什么时间核实</v>
+        <v>待核实点明确由谁在什么时</v>
       </c>
       <c r="D8" t="str">
         <v>待核实点明确由谁在什么时间核实</v>
@@ -1550,7 +1571,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_RX_02</v>
+        <v>HS_RX_002</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
@@ -1582,13 +1603,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_RX_03</v>
+        <v>HS_RX_003</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>本周主动做一次与问题无关的正向接触</v>
+        <v>本周主动做一次与问题无关</v>
       </c>
       <c r="D10" t="str">
         <v>本周主动做一次与问题无关的正向接触</v>
@@ -1614,13 +1635,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_RX_03</v>
+        <v>HS_RX_003</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>只反馈孩子的一个具体进步，不带任何请求</v>
+        <v>只反馈孩子的一个具体进步</v>
       </c>
       <c r="D11" t="str">
         <v>只反馈孩子的一个具体进步，不带任何请求</v>
@@ -1646,13 +1667,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_RX_03</v>
+        <v>HS_RX_003</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
+        <v>两周内累计三次正向接触后</v>
       </c>
       <c r="D12" t="str">
         <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
@@ -1678,13 +1699,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_RX_03</v>
+        <v>HS_RX_003</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>每次接触后记录家长的回应变化</v>
+        <v>每次接触后记录家长的回应</v>
       </c>
       <c r="D13" t="str">
         <v>每次接触后记录家长的回应变化</v>
@@ -1710,13 +1731,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>把原本的请求拆到一周内能完成的最小动作</v>
+        <v>把原本的请求拆到一周内能</v>
       </c>
       <c r="D14" t="str">
         <v>把原本的请求拆到一周内能完成的最小动作</v>
@@ -1742,13 +1763,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>明确「做什么、什么时候、怎么反馈」三件事</v>
+        <v>明确「做什么、什么时候、</v>
       </c>
       <c r="D15" t="str">
         <v>明确「做什么、什么时候、怎么反馈」三件事</v>
@@ -1774,7 +1795,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
@@ -1806,13 +1827,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HS_RX_04</v>
+        <v>HS_RX_004</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>连续两次完成后再提高一点要求</v>
+        <v>连续两次完成后再提高一点</v>
       </c>
       <c r="D17" t="str">
         <v>连续两次完成后再提高一点要求</v>
@@ -1838,13 +1859,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>与家长约定固定的反馈时间点，如每周五下午</v>
+        <v>与家长约定固定的反馈时间</v>
       </c>
       <c r="D18" t="str">
         <v>与家长约定固定的反馈时间点，如每周五下午</v>
@@ -1870,13 +1891,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>明确每次反馈包含哪三项内容</v>
+        <v>明确每次反馈包含哪三项内</v>
       </c>
       <c r="D19" t="str">
         <v>明确每次反馈包含哪三项内容</v>
@@ -1902,13 +1923,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>约定非紧急事项统一在反馈时处理</v>
+        <v>约定非紧急事项统一在反馈</v>
       </c>
       <c r="D20" t="str">
         <v>约定非紧急事项统一在反馈时处理</v>
@@ -1934,7 +1955,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HS_RX_05</v>
+        <v>HS_RX_005</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
@@ -1966,13 +1987,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>只承诺一件本周确定能做到的小事</v>
+        <v>只承诺一件本周确定能做到</v>
       </c>
       <c r="D22" t="str">
         <v>只承诺一件本周确定能做到的小事</v>
@@ -1998,7 +2019,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
@@ -2030,7 +2051,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
@@ -2062,13 +2083,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HS_RX_06</v>
+        <v>HS_RX_006</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>连续兑现三次后再讨论更大的议题</v>
+        <v>连续兑现三次后再讨论更大</v>
       </c>
       <c r="D25" t="str">
         <v>连续兑现三次后再讨论更大的议题</v>
@@ -2094,13 +2115,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B26" t="str">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>立即停止单独沟通，不再单方回应</v>
+        <v>立即停止单独沟通，不再单</v>
       </c>
       <c r="D26" t="str">
         <v>立即停止单独沟通，不再单方回应</v>
@@ -2126,13 +2147,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B27" t="str">
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>完整保存聊天记录、通话记录和相关材料</v>
+        <v>完整保存聊天记录、通话记</v>
       </c>
       <c r="D27" t="str">
         <v>完整保存聊天记录、通话记录和相关材料</v>
@@ -2158,13 +2179,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B28" t="str">
         <v>3</v>
       </c>
       <c r="C28" t="str">
-        <v>当天上报年级组长并填写事件说明</v>
+        <v>当天上报年级组长并填写事</v>
       </c>
       <c r="D28" t="str">
         <v>当天上报年级组长并填写事件说明</v>
@@ -2190,13 +2211,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B29" t="str">
         <v>4</v>
       </c>
       <c r="C29" t="str">
-        <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+        <v>后续沟通全部由年级组长或</v>
       </c>
       <c r="D29" t="str">
         <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
@@ -2256,7 +2277,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_07</v>
+        <v>HS_RX_007</v>
       </c>
       <c r="B2" t="str">
         <v>事件已进入法律程序</v>

--- a/business-libraries/test-data/home_school/tool.xlsx
+++ b/business-libraries/test-data/home_school/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>先跟后带话术卡</v>
       </c>
       <c r="C2" t="str">
-        <v>先跟后带</v>
+        <v>先跟后带话术卡</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -540,25 +540,22 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="K2" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界问题</v>
       </c>
       <c r="L2" t="str">
-        <v>home_school,container</v>
+        <v>home_school,boundary</v>
       </c>
       <c r="M2" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D2</v>
       </c>
       <c r="N2" t="str">
         <v>在不认同内容的前提下承接情绪</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">先复述家长的担心，用他的原话
-表达理解而非认同：「我能感受到您现在很担心」
-把话题引向可核实的事实
-约定一个具体的下一步和反馈时间</v>
+      <c r="O2" t="str">
+        <v>先复述家长的担心，用他的原话；表达理解而非认同：「我能感受到您现在很担心」；把话题引向可核实的事实；约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="P2" t="str">
         <v>我能感受到您现在很担心。我们先把事实逐项核实，再一起决定下一步。</v>
@@ -615,24 +612,24 @@
         <v/>
       </c>
       <c r="AH2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>事实边界记录表</v>
       </c>
       <c r="C3" t="str">
-        <v>事实记录</v>
+        <v>事实边界记录表</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -653,25 +650,22 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_01</v>
       </c>
       <c r="K3" t="str">
-        <v>沟通冲突升级</v>
+        <v>沟通质量薄弱</v>
       </c>
       <c r="L3" t="str">
-        <v>home_school,conflict</v>
+        <v>home_school,communication</v>
       </c>
       <c r="M3" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="N3" t="str">
         <v>把争议从情绪层面拉回可核实的事实</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">分三栏记录：家长诉求 / 已核实事实 / 待核实点
-每一条都注明时间、在场人和信息来源
-待核实点明确由谁在什么时间核实
-核实结果书面反馈给家长</v>
+      <c r="O3" t="str">
+        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点；每一条都注明时间、在场人和信息来源；待核实点明确由谁在什么时间核实；核实结果书面反馈给家长</v>
       </c>
       <c r="P3" t="str">
         <v>这一条我需要先向任课老师核实，明天下午三点前给您答复。</v>
@@ -728,24 +722,24 @@
         <v/>
       </c>
       <c r="AH3" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>沟通容器修复计划</v>
       </c>
       <c r="C4" t="str">
-        <v>容器修复</v>
+        <v>沟通容器修复计划</v>
       </c>
       <c r="D4" t="str">
         <v>home_school</v>
@@ -766,25 +760,22 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>HS_AT_CONTAINER</v>
+        <v>HS_AT_02</v>
       </c>
       <c r="K4" t="str">
-        <v>关系容器不足</v>
+        <v>角色边界问题</v>
       </c>
       <c r="L4" t="str">
-        <v>home_school,container</v>
+        <v>home_school,boundary</v>
       </c>
       <c r="M4" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D2</v>
       </c>
       <c r="N4" t="str">
         <v>重建可承载坦诚讨论的关系基础</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">本周主动做一次与问题无关的正向接触
-只反馈孩子的一个具体进步，不带任何请求
-两周内累计三次正向接触后，再谈需要讨论的问题
-每次接触后记录家长的回应变化</v>
+      <c r="O4" t="str">
+        <v>本周主动做一次与问题无关的正向接触；只反馈孩子的一个具体进步，不带任何请求；两周内累计三次正向接触后，再谈需要讨论的问题；每次接触后记录家长的回应变化</v>
       </c>
       <c r="P4" t="str">
         <v>今天想跟您说件小事，孩子这周主动帮同学讲了一道题。</v>
@@ -841,24 +832,24 @@
         <v/>
       </c>
       <c r="AH4" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>最小请求约定法</v>
       </c>
       <c r="C5" t="str">
-        <v>最小请求</v>
+        <v>最小请求约定法</v>
       </c>
       <c r="D5" t="str">
         <v>home_school</v>
@@ -879,25 +870,22 @@
         <v>low</v>
       </c>
       <c r="J5" t="str">
-        <v>HS_AT_COOP</v>
+        <v>HS_AT_05</v>
       </c>
       <c r="K5" t="str">
-        <v>配合度不足</v>
+        <v>参与效能不足</v>
       </c>
       <c r="L5" t="str">
         <v>home_school,cooperation</v>
       </c>
       <c r="M5" t="str">
-        <v>HS_COOP</v>
+        <v>HS_S1D5</v>
       </c>
       <c r="N5" t="str">
         <v>把配合请求缩小到可完成的尺度</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">把原本的请求拆到一周内能完成的最小动作
-明确「做什么、什么时候、怎么反馈」三件事
-完成后当天给出正向反馈
-连续两次完成后再提高一点要求</v>
+      <c r="O5" t="str">
+        <v>把原本的请求拆到一周内能完成的最小动作；明确「做什么、什么时候、怎么反馈」三件事；完成后当天给出正向反馈；连续两次完成后再提高一点要求</v>
       </c>
       <c r="P5" t="str">
         <v>这周只请您做一件事：晚饭后问一句今天数学课听懂了多少，周五告诉我他怎么说。</v>
@@ -939,7 +927,7 @@
         <v>连续两周完成约定</v>
       </c>
       <c r="AC5" t="str">
-        <v>连续两次未完成（改用 HS_RX_003）</v>
+        <v>连续两次未完成（改用承诺兑现清单）</v>
       </c>
       <c r="AD5" t="str">
         <v>准备记录表</v>
@@ -954,24 +942,24 @@
         <v/>
       </c>
       <c r="AH5" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>定期反馈节奏表</v>
       </c>
       <c r="C6" t="str">
-        <v>反馈节奏</v>
+        <v>定期反馈节奏表</v>
       </c>
       <c r="D6" t="str">
         <v>home_school</v>
@@ -992,25 +980,22 @@
         <v>medium</v>
       </c>
       <c r="J6" t="str">
-        <v>HS_AT_ANXIETY</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="K6" t="str">
-        <v>家长焦虑过载</v>
+        <v>信任关系薄弱</v>
       </c>
       <c r="L6" t="str">
-        <v>home_school,anxiety</v>
+        <v>home_school,trust</v>
       </c>
       <c r="M6" t="str">
-        <v>HS_ANXIETY</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="N6" t="str">
         <v>用可预期的信息节奏降低焦虑</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">与家长约定固定的反馈时间点，如每周五下午
-明确每次反馈包含哪三项内容
-约定非紧急事项统一在反馈时处理
-紧急情况的判断标准写清楚</v>
+      <c r="O6" t="str">
+        <v>与家长约定固定的反馈时间点，如每周五下午；明确每次反馈包含哪三项内容；约定非紧急事项统一在反馈时处理；紧急情况的判断标准写清楚</v>
       </c>
       <c r="P6" t="str">
         <v>我每周五下午会把这三件事同步给您，中间如果有紧急情况我会随时联系。</v>
@@ -1067,24 +1052,24 @@
         <v/>
       </c>
       <c r="AH6" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>承诺兑现清单</v>
       </c>
       <c r="C7" t="str">
-        <v>承诺兑现</v>
+        <v>承诺兑现清单</v>
       </c>
       <c r="D7" t="str">
         <v>home_school</v>
@@ -1105,25 +1090,22 @@
         <v>medium</v>
       </c>
       <c r="J7" t="str">
-        <v>HS_AT_TRUST</v>
+        <v>HS_AT_04</v>
       </c>
       <c r="K7" t="str">
-        <v>信任基础薄弱</v>
+        <v>信任关系薄弱</v>
       </c>
       <c r="L7" t="str">
         <v>home_school,trust</v>
       </c>
       <c r="M7" t="str">
-        <v>HS_TRUST</v>
+        <v>HS_S1D4</v>
       </c>
       <c r="N7" t="str">
         <v>用可验证的行为重建信任</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">只承诺一件本周确定能做到的小事
-明确完成时间和验证方式
-按时完成并主动告知结果
-连续兑现三次后再讨论更大的议题</v>
+      <c r="O7" t="str">
+        <v>只承诺一件本周确定能做到的小事；明确完成时间和验证方式；按时完成并主动告知结果；连续兑现三次后再讨论更大的议题</v>
       </c>
       <c r="P7" t="str">
         <v>这周我会安排他坐到第二排，周五我告诉您效果怎么样。</v>
@@ -1180,24 +1162,24 @@
         <v/>
       </c>
       <c r="AH7" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B8" t="str">
         <v>E 级保护通道操作卡</v>
       </c>
       <c r="C8" t="str">
-        <v>E级保护</v>
+        <v>E 级保护通道操</v>
       </c>
       <c r="D8" t="str">
         <v>home_school</v>
@@ -1218,25 +1200,22 @@
         <v>crisis</v>
       </c>
       <c r="J8" t="str">
-        <v>HS_AT_CONFLICT</v>
+        <v>HS_AT_06</v>
       </c>
       <c r="K8" t="str">
-        <v>沟通冲突升级</v>
+        <v>危机响应风险</v>
       </c>
       <c r="L8" t="str">
-        <v>home_school,conflict,crisis</v>
+        <v>home_school,crisis</v>
       </c>
       <c r="M8" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="N8" t="str">
         <v>保护教师并把处置转到学校层面</v>
       </c>
-      <c r="O8" t="str" xml:space="preserve">
-        <v xml:space="preserve">立即停止单独沟通，不再单方回应
-完整保存聊天记录、通话记录和相关材料
-当天上报年级组长并填写事件说明
-后续沟通全部由年级组长或校方主导，教师只提供事实</v>
+      <c r="O8" t="str">
+        <v>立即停止单独沟通，不再单方回应；完整保存聊天记录、通话记录和相关材料；当天上报年级组长并填写事件说明；后续沟通全部由年级组长或校方主导，教师只提供事实</v>
       </c>
       <c r="P8" t="str">
         <v>这件事我需要请年级组长一起来处理，我们另约时间当面谈。</v>
@@ -1293,10 +1272,10 @@
         <v/>
       </c>
       <c r="AH8" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
       <c r="AI8" t="str">
-        <v>1.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -1347,13 +1326,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>先复述家长的担心，用他的</v>
+        <v>先复述家长的担心，用他的原话</v>
       </c>
       <c r="D2" t="str">
         <v>先复述家长的担心，用他的原话</v>
@@ -1379,13 +1358,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>表达理解而非认同：「我能</v>
+        <v>表达理解而非认同：「我能感受到您现在很担心」</v>
       </c>
       <c r="D3" t="str">
         <v>表达理解而非认同：「我能感受到您现在很担心」</v>
@@ -1411,7 +1390,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
@@ -1443,13 +1422,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_RX_001</v>
+        <v>HS_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>约定一个具体的下一步和反</v>
+        <v>约定一个具体的下一步和反馈时间</v>
       </c>
       <c r="D5" t="str">
         <v>约定一个具体的下一步和反馈时间</v>
@@ -1475,13 +1454,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>分三栏记录：家长诉求 /</v>
+        <v>分三栏记录：家长诉求 / 已核实事实 / 待核实</v>
       </c>
       <c r="D6" t="str">
         <v>分三栏记录：家长诉求 / 已核实事实 / 待核实点</v>
@@ -1507,13 +1486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>每一条都注明时间、在场人</v>
+        <v>每一条都注明时间、在场人和信息来源</v>
       </c>
       <c r="D7" t="str">
         <v>每一条都注明时间、在场人和信息来源</v>
@@ -1539,13 +1518,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>待核实点明确由谁在什么时</v>
+        <v>待核实点明确由谁在什么时间核实</v>
       </c>
       <c r="D8" t="str">
         <v>待核实点明确由谁在什么时间核实</v>
@@ -1571,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_RX_002</v>
+        <v>HS_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
@@ -1603,13 +1582,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>本周主动做一次与问题无关</v>
+        <v>本周主动做一次与问题无关的正向接触</v>
       </c>
       <c r="D10" t="str">
         <v>本周主动做一次与问题无关的正向接触</v>
@@ -1635,13 +1614,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>只反馈孩子的一个具体进步</v>
+        <v>只反馈孩子的一个具体进步，不带任何请求</v>
       </c>
       <c r="D11" t="str">
         <v>只反馈孩子的一个具体进步，不带任何请求</v>
@@ -1667,13 +1646,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>两周内累计三次正向接触后</v>
+        <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
       </c>
       <c r="D12" t="str">
         <v>两周内累计三次正向接触后，再谈需要讨论的问题</v>
@@ -1699,13 +1678,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_RX_003</v>
+        <v>HS_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>每次接触后记录家长的回应</v>
+        <v>每次接触后记录家长的回应变化</v>
       </c>
       <c r="D13" t="str">
         <v>每次接触后记录家长的回应变化</v>
@@ -1731,13 +1710,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>把原本的请求拆到一周内能</v>
+        <v>把原本的请求拆到一周内能完成的最小动作</v>
       </c>
       <c r="D14" t="str">
         <v>把原本的请求拆到一周内能完成的最小动作</v>
@@ -1763,13 +1742,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>明确「做什么、什么时候、</v>
+        <v>明确「做什么、什么时候、怎么反馈」三件事</v>
       </c>
       <c r="D15" t="str">
         <v>明确「做什么、什么时候、怎么反馈」三件事</v>
@@ -1795,7 +1774,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
@@ -1827,13 +1806,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HS_RX_004</v>
+        <v>HS_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>连续两次完成后再提高一点</v>
+        <v>连续两次完成后再提高一点要求</v>
       </c>
       <c r="D17" t="str">
         <v>连续两次完成后再提高一点要求</v>
@@ -1859,13 +1838,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>与家长约定固定的反馈时间</v>
+        <v>与家长约定固定的反馈时间点，如每周五下午</v>
       </c>
       <c r="D18" t="str">
         <v>与家长约定固定的反馈时间点，如每周五下午</v>
@@ -1891,13 +1870,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>明确每次反馈包含哪三项内</v>
+        <v>明确每次反馈包含哪三项内容</v>
       </c>
       <c r="D19" t="str">
         <v>明确每次反馈包含哪三项内容</v>
@@ -1923,13 +1902,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>约定非紧急事项统一在反馈</v>
+        <v>约定非紧急事项统一在反馈时处理</v>
       </c>
       <c r="D20" t="str">
         <v>约定非紧急事项统一在反馈时处理</v>
@@ -1955,7 +1934,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HS_RX_005</v>
+        <v>HS_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
@@ -1987,13 +1966,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>只承诺一件本周确定能做到</v>
+        <v>只承诺一件本周确定能做到的小事</v>
       </c>
       <c r="D22" t="str">
         <v>只承诺一件本周确定能做到的小事</v>
@@ -2019,7 +1998,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
@@ -2051,7 +2030,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
@@ -2083,13 +2062,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HS_RX_006</v>
+        <v>HS_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>连续兑现三次后再讨论更大</v>
+        <v>连续兑现三次后再讨论更大的议题</v>
       </c>
       <c r="D25" t="str">
         <v>连续兑现三次后再讨论更大的议题</v>
@@ -2115,13 +2094,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B26" t="str">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>立即停止单独沟通，不再单</v>
+        <v>立即停止单独沟通，不再单方回应</v>
       </c>
       <c r="D26" t="str">
         <v>立即停止单独沟通，不再单方回应</v>
@@ -2147,13 +2126,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B27" t="str">
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>完整保存聊天记录、通话记</v>
+        <v>完整保存聊天记录、通话记录和相关材料</v>
       </c>
       <c r="D27" t="str">
         <v>完整保存聊天记录、通话记录和相关材料</v>
@@ -2179,13 +2158,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B28" t="str">
         <v>3</v>
       </c>
       <c r="C28" t="str">
-        <v>当天上报年级组长并填写事</v>
+        <v>当天上报年级组长并填写事件说明</v>
       </c>
       <c r="D28" t="str">
         <v>当天上报年级组长并填写事件说明</v>
@@ -2211,13 +2190,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B29" t="str">
         <v>4</v>
       </c>
       <c r="C29" t="str">
-        <v>后续沟通全部由年级组长或</v>
+        <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
       </c>
       <c r="D29" t="str">
         <v>后续沟通全部由年级组长或校方主导，教师只提供事实</v>
@@ -2277,7 +2256,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_RX_007</v>
+        <v>HS_RX_07</v>
       </c>
       <c r="B2" t="str">
         <v>事件已进入法律程序</v>
@@ -2295,7 +2274,7 @@
         <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>家校沟通合作手册v1</v>
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
       </c>
     </row>
   </sheetData>
